--- a/Data/Export/Common/ItemType_道具类型.xlsx
+++ b/Data/Export/Common/ItemType_道具类型.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\sango_infinity\Data\Export\Common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A47F86-D843-4EEB-B053-A579282DA21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB73BBA-F280-455E-9F70-AE78DF47A80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemTypes" sheetId="36" r:id="rId1"/>
@@ -178,10 +178,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>刀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -316,6 +312,10 @@
   </si>
   <si>
     <t>storeKind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>戟</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -820,31 +820,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AD69"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" style="2" customWidth="1"/>
-    <col min="6" max="7" width="9.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="2" customWidth="1"/>
+    <col min="6" max="7" width="9.625" style="2" customWidth="1"/>
     <col min="8" max="8" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="54.6640625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="21.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="15.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="54.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="21.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.375" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="8.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="8.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.625" style="2" bestFit="1" customWidth="1"/>
     <col min="25" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -861,28 +861,28 @@
       <c r="F1" s="17"/>
       <c r="G1" s="17"/>
       <c r="H1" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>8</v>
       </c>
       <c r="L1" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="P1" s="13"/>
       <c r="Q1" s="13"/>
@@ -900,7 +900,7 @@
       <c r="AC1" s="8"/>
       <c r="AD1" s="6"/>
     </row>
-    <row r="2" spans="1:30" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -916,7 +916,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -936,7 +936,7 @@
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
     </row>
-    <row r="3" spans="1:30" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -950,22 +950,22 @@
         <v>14</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>10</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K3" s="12" t="s">
         <v>12</v>
@@ -974,13 +974,13 @@
         <v>11</v>
       </c>
       <c r="M3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
@@ -998,7 +998,7 @@
       <c r="AC3" s="7"/>
       <c r="AD3" s="7"/>
     </row>
-    <row r="4" spans="1:30" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G4" s="16" t="s">
         <v>5</v>
@@ -1027,7 +1027,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K4" s="16" t="s">
         <v>3</v>
@@ -1054,7 +1054,7 @@
       <c r="W4" s="15"/>
       <c r="X4" s="15"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4" t="s">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>38</v>
@@ -1095,7 +1095,7 @@
       <c r="AA5" s="4"/>
       <c r="AC5" s="4"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1110,7 +1110,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4" t="s">
@@ -1120,10 +1120,10 @@
         <v>35</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
@@ -1139,12 +1139,12 @@
       <c r="AA6" s="4"/>
       <c r="AC6" s="4"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
@@ -1153,7 +1153,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4" t="s">
@@ -1163,10 +1163,10 @@
         <v>35</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
@@ -1182,7 +1182,7 @@
       <c r="AA7" s="4"/>
       <c r="AC7" s="4"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.15">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4" t="s">
@@ -1206,10 +1206,10 @@
         <v>35</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
@@ -1225,7 +1225,7 @@
       <c r="AA8" s="4"/>
       <c r="AC8" s="4"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4" t="s">
@@ -1249,10 +1249,10 @@
         <v>36</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
@@ -1268,7 +1268,7 @@
       <c r="AA9" s="4"/>
       <c r="AC9" s="4"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -1279,13 +1279,13 @@
         <v>3</v>
       </c>
       <c r="E10" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4" t="s">
@@ -1295,13 +1295,13 @@
         <v>37</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
@@ -1317,7 +1317,7 @@
       <c r="AA10" s="4"/>
       <c r="AC10" s="4"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -1328,10 +1328,10 @@
         <v>3</v>
       </c>
       <c r="E11" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H11" s="4">
         <v>1</v>
@@ -1343,13 +1343,13 @@
         <v>37</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
@@ -1365,7 +1365,7 @@
       <c r="AA11" s="4"/>
       <c r="AC11" s="4"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -1376,13 +1376,13 @@
         <v>3</v>
       </c>
       <c r="E12" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4" t="s">
@@ -1392,13 +1392,13 @@
         <v>37</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
@@ -1414,7 +1414,7 @@
       <c r="AA12" s="4"/>
       <c r="AC12" s="4"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -1425,10 +1425,10 @@
         <v>3</v>
       </c>
       <c r="E13" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H13" s="4">
         <v>2</v>
@@ -1440,13 +1440,13 @@
         <v>37</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
@@ -1462,7 +1462,7 @@
       <c r="AA13" s="4"/>
       <c r="AC13" s="4"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -1473,10 +1473,10 @@
         <v>4</v>
       </c>
       <c r="E14" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="4" t="s">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>38</v>
@@ -1503,7 +1503,7 @@
       <c r="AA14" s="4"/>
       <c r="AC14" s="4"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -1514,13 +1514,13 @@
         <v>4</v>
       </c>
       <c r="E15" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4" t="s">
@@ -1530,13 +1530,13 @@
         <v>38</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
@@ -1552,7 +1552,7 @@
       <c r="AA15" s="4"/>
       <c r="AC15" s="4"/>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -1563,10 +1563,10 @@
         <v>4</v>
       </c>
       <c r="E16" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H16" s="4">
         <v>2</v>
@@ -1578,13 +1578,13 @@
         <v>38</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
@@ -1600,7 +1600,7 @@
       <c r="AA16" s="4"/>
       <c r="AC16" s="4"/>
     </row>
-    <row r="17" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -1622,7 +1622,7 @@
       <c r="AA17" s="4"/>
       <c r="AC17" s="4"/>
     </row>
-    <row r="18" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -1644,7 +1644,7 @@
       <c r="AA18" s="4"/>
       <c r="AC18" s="4"/>
     </row>
-    <row r="19" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -1657,7 +1657,7 @@
       <c r="AA19" s="4"/>
       <c r="AC19" s="4"/>
     </row>
-    <row r="20" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -1670,7 +1670,7 @@
       <c r="AA20" s="4"/>
       <c r="AC20" s="4"/>
     </row>
-    <row r="21" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -1683,7 +1683,7 @@
       <c r="AA21" s="4"/>
       <c r="AC21" s="4"/>
     </row>
-    <row r="22" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -1696,7 +1696,7 @@
       <c r="AA22" s="4"/>
       <c r="AC22" s="4"/>
     </row>
-    <row r="23" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -1709,7 +1709,7 @@
       <c r="AA23" s="4"/>
       <c r="AC23" s="4"/>
     </row>
-    <row r="24" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -1722,7 +1722,7 @@
       <c r="AA24" s="4"/>
       <c r="AC24" s="4"/>
     </row>
-    <row r="25" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -1735,7 +1735,7 @@
       <c r="AA25" s="4"/>
       <c r="AC25" s="4"/>
     </row>
-    <row r="26" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -1748,7 +1748,7 @@
       <c r="AA26" s="4"/>
       <c r="AC26" s="4"/>
     </row>
-    <row r="27" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -1761,7 +1761,7 @@
       <c r="AA27" s="4"/>
       <c r="AC27" s="4"/>
     </row>
-    <row r="28" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -1774,7 +1774,7 @@
       <c r="AA28" s="4"/>
       <c r="AC28" s="4"/>
     </row>
-    <row r="29" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -1787,7 +1787,7 @@
       <c r="AA29" s="4"/>
       <c r="AC29" s="4"/>
     </row>
-    <row r="30" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
@@ -1800,7 +1800,7 @@
       <c r="AA30" s="4"/>
       <c r="AC30" s="4"/>
     </row>
-    <row r="31" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -1813,7 +1813,7 @@
       <c r="AA31" s="4"/>
       <c r="AC31" s="4"/>
     </row>
-    <row r="32" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -1826,7 +1826,7 @@
       <c r="AA32" s="4"/>
       <c r="AC32" s="4"/>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -1839,7 +1839,7 @@
       <c r="AA33" s="4"/>
       <c r="AC33" s="4"/>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -1852,7 +1852,7 @@
       <c r="AA34" s="4"/>
       <c r="AC34" s="4"/>
     </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -1865,7 +1865,7 @@
       <c r="AA35" s="4"/>
       <c r="AC35" s="4"/>
     </row>
-    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -1878,7 +1878,7 @@
       <c r="AA36" s="4"/>
       <c r="AC36" s="4"/>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -1890,7 +1890,7 @@
       <c r="AA37" s="4"/>
       <c r="AC37" s="4"/>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.15">
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="H38" s="4"/>
@@ -1901,7 +1901,7 @@
       <c r="AA38" s="4"/>
       <c r="AC38" s="4"/>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.15">
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="H39" s="4"/>
@@ -1912,7 +1912,7 @@
       <c r="AA39" s="4"/>
       <c r="AC39" s="4"/>
     </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:29" x14ac:dyDescent="0.15">
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="H40" s="4"/>
@@ -1923,7 +1923,7 @@
       <c r="AA40" s="4"/>
       <c r="AC40" s="4"/>
     </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:29" x14ac:dyDescent="0.15">
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="H41" s="4"/>
@@ -1934,7 +1934,7 @@
       <c r="AA41" s="4"/>
       <c r="AC41" s="4"/>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.15">
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="H42" s="4"/>
@@ -1945,7 +1945,7 @@
       <c r="AA42" s="4"/>
       <c r="AC42" s="4"/>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.15">
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="H43" s="4"/>
@@ -1956,7 +1956,7 @@
       <c r="AA43" s="4"/>
       <c r="AC43" s="4"/>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.15">
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="H44" s="4"/>
@@ -1967,7 +1967,7 @@
       <c r="AA44" s="4"/>
       <c r="AC44" s="4"/>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.15">
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="H45" s="4"/>
@@ -1978,7 +1978,7 @@
       <c r="AA45" s="4"/>
       <c r="AC45" s="4"/>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.15">
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="H46" s="4"/>
@@ -1988,161 +1988,161 @@
       <c r="AA46" s="4"/>
       <c r="AC46" s="4"/>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.15">
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.15">
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="50" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
     </row>
-    <row r="51" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
     </row>
-    <row r="52" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
     </row>
-    <row r="53" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
     </row>
-    <row r="54" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
     </row>
-    <row r="55" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
     </row>
-    <row r="56" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
     </row>
-    <row r="57" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
     </row>
-    <row r="58" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
     </row>
-    <row r="59" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
     </row>
-    <row r="60" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
     </row>
-    <row r="61" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
       <c r="J61" s="4"/>
     </row>
-    <row r="62" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
     </row>
-    <row r="63" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
     </row>
-    <row r="64" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
     </row>
-    <row r="65" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
       <c r="J65" s="4"/>
     </row>
-    <row r="66" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
     </row>
-    <row r="67" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
     </row>
-    <row r="68" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
     </row>
-    <row r="69" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:10" x14ac:dyDescent="0.15">
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="H69" s="4"/>
